--- a/data/trans_bre/IP07_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP07_R2-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-5,01</t>
+          <t>-4,93</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-68,38%</t>
+          <t>-66,28%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 0,76</t>
+          <t>-4,21; 1,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 3,19</t>
+          <t>-3,9; 3,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 1,19</t>
+          <t>-5,63; 0,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 0,69</t>
+          <t>-12,84; 0,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-70,73; 181,82</t>
+          <t>-74,71; 178,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-89,75; 102,66</t>
+          <t>-92,06; 89,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 160,67</t>
+          <t>-100,0; 117,94</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-5,07%</t>
+          <t>-2,0%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,92; -0,84</t>
+          <t>-5,01; -0,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,18</t>
+          <t>-0,11; 3,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 4,0</t>
+          <t>-0,47; 3,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 2,17</t>
+          <t>-2,2; 2,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -21,26</t>
+          <t>-94,96; -26,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,81; inf</t>
+          <t>-43,58; 1484,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-53,41; 1088,61</t>
+          <t>-50,63; 1082,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-88,51; 420,0</t>
+          <t>-88,11; 411,34</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 0,14</t>
+          <t>-7,97; -0,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 2,08</t>
+          <t>-4,0; 1,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 1,27</t>
+          <t>-3,63; 1,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 4,22</t>
+          <t>-2,28; 3,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-91,54; 16,74</t>
+          <t>-91,21; 15,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-82,95; 176,22</t>
+          <t>-85,85; 155,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-87,2; 192,73</t>
+          <t>-89,62; 133,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-59,36; 377,63</t>
+          <t>-61,22; 333,03</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>128,96%</t>
+          <t>34,0%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 3,09</t>
+          <t>-2,5; 3,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 1,43</t>
+          <t>-4,88; 1,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 2,4</t>
+          <t>-2,9; 2,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 9,6</t>
+          <t>-1,56; 3,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,49; 207,7</t>
+          <t>-60,57; 181,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,19; 94,44</t>
+          <t>-85,58; 98,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-81,69; 291,42</t>
+          <t>-83,57; 283,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,07; 1169,56</t>
+          <t>-65,77; 325,74</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,14; -0,52</t>
+          <t>-3,3; -0,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,2</t>
+          <t>-1,45; 1,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,07</t>
+          <t>-1,38; 1,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 3,91</t>
+          <t>-1,53; 1,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-72,74; -13,8</t>
+          <t>-74,28; -14,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,71; 64,05</t>
+          <t>-47,45; 72,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-50,0; 74,47</t>
+          <t>-51,57; 70,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-32,22; 182,94</t>
+          <t>-46,82; 92,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP07_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP07_R2-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,19</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,28</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,88</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-4,93</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-54,08%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-8,05%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-50,98%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-66,28%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.18671017077946</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.2836782250131301</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.876359395609744</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-4.926635582049505</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.5407577995360622</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.08051486223753457</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.5097875840350564</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.6627884959518332</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-4,21; 1,2</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-3,9; 3,12</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-5,63; 0,98</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-12,84; 0,96</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-74,71; 178,34</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-92,06; 89,11</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 117,94</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-4.205714550244742</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.901804908368588</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.626868038764182</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-12.8383730365946</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>-0.7471143589485965</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.9206367175732267</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.195677652719746</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.12078706350073</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9774218136277049</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0.9560978748367934</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="n">
+        <v>1.78339858379613</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.8910627957769814</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.179412729436395</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-2,71</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,34</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-77,71%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>173,77%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>135,36%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-2,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,01; -0,84</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-0,11; 3,42</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-0,47; 3,68</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,2; 2,65</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-94,96; -26,28</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-43,58; 1484,92</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-50,63; 1082,4</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-88,11; 411,34</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-2.711136768752189</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.304672176171931</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.335777350679074</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.03566738850392139</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.7770548419366988</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1.737698649347407</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>1.353569671350318</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.01995735644073562</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,48</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,84</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,98</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,82</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-62,2%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-27,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-40,18%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>31,36%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.012464358897516</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.1050079330815572</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.4695700578499479</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.204325405716902</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.949560432917232</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4358171609180705</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.5063365815925501</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.8810678598879736</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-7,97; -0,17</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,0; 1,83</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-3,63; 1,31</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-2,28; 3,97</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-91,21; 15,19</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-85,85; 155,72</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-89,62; 133,32</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-61,22; 333,03</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-0.8448287967078225</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.421089017350554</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.678163066223833</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.65137406414318</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.2627554488897166</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>14.84918563541214</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>10.82400712939063</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>4.113375901549763</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +815,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,67</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,62</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-44,68%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-9,38%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>34,0%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-3.482811108354203</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.8446156595423474</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.9803856308421602</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.8159591174406986</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.6219584886176048</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.2740843208666511</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.4018144031638349</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.313566838955098</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,5; 3,01</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,88; 1,31</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,9; 2,26</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,56; 3,06</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-60,57; 181,54</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-85,58; 98,47</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-83,57; 283,92</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-65,77; 325,74</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-7.973954493325684</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.999630109336209</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.632452078064684</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.275861959173244</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.9120871270181944</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.8584883508214908</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.8961667599084825</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.612169253500611</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-0.1729263029617232</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.834719975251976</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.312537341804611</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.967248914444932</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1518788061093289</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.557242328515387</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.333175496922859</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>3.330267786373091</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.09991385900459566</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.669280380499483</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.2073832639270398</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.6217459767611251</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.0339558377560683</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.4467730620863976</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.09382984159913463</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.3400086658374084</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.498177564012114</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.878593604933876</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.903918627519279</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.560978578883963</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.605749009540722</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.855761270396372</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.835667921978244</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.6576937694158389</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.011787859143132</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.307011416219256</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.264917521024797</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3.060812493189647</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.815434248012878</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.9846612635029145</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.839227921177298</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>3.257393956092846</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,82</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-51,56%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-6,16%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-8,33%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-3,3; -0,54</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,45; 1,22</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,38; 1,02</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,53; 1,54</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-74,28; -14,75</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-47,45; 72,13</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-51,57; 70,58</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-46,82; 92,64</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-1.82031952900089</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.1538265050976439</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.1740796697692185</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.1189184607911353</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.5156376531532615</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.06159639618925046</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.08334277861835468</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.04865030289343336</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-3.295542617938637</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.451244335341537</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.379536634705319</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.53279939678702</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.7427642703977334</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.474489175088241</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.5157241096654185</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.4682405516257258</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>-0.5445886347575007</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.223982574820716</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.021592243925387</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.540648846660291</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-0.1474772761140006</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.7213148389015263</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.7057769517258944</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.9263900943238097</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1113,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
